--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-CapabilityStatement-Feature.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-CapabilityStatement-Feature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="195">
   <si>
     <t>Property</t>
   </si>
@@ -528,6 +528,9 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -1914,7 +1917,7 @@
         <v>86</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>131</v>
@@ -2484,9 +2487,11 @@
       <c r="M15" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N15" s="2"/>
+      <c r="N15" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2535,7 +2540,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2550,15 +2555,15 @@
         <v>131</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2581,19 +2586,19 @@
         <v>104</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2642,7 +2647,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2657,18 +2662,18 @@
         <v>131</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>76</v>
@@ -2693,13 +2698,13 @@
         <v>94</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2769,7 +2774,7 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>109</v>
@@ -2872,7 +2877,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>111</v>
@@ -2975,7 +2980,7 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>115</v>
@@ -3018,7 +3023,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>76</v>
@@ -3080,7 +3085,7 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>123</v>
@@ -3106,16 +3111,16 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3174,7 +3179,7 @@
         <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>131</v>
@@ -3316,13 +3321,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3382,7 +3387,7 @@
         <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>131</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-CapabilityStatement-Feature.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-CapabilityStatement-Feature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -528,9 +528,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -1917,7 +1914,7 @@
         <v>86</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>131</v>
@@ -2487,11 +2484,9 @@
       <c r="M15" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2540,7 +2535,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2555,15 +2550,15 @@
         <v>131</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2586,19 +2581,19 @@
         <v>104</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2647,7 +2642,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2662,18 +2657,18 @@
         <v>131</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>76</v>
@@ -2698,13 +2693,13 @@
         <v>94</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2774,7 +2769,7 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>109</v>
@@ -2877,7 +2872,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>111</v>
@@ -2980,7 +2975,7 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>115</v>
@@ -3023,7 +3018,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>76</v>
@@ -3085,7 +3080,7 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>123</v>
@@ -3111,16 +3106,16 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3179,7 +3174,7 @@
         <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>131</v>
@@ -3321,13 +3316,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3387,7 +3382,7 @@
         <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>131</v>
